--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_347_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_347_R35.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5566</v>
+        <v>11.8329</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9265</v>
+        <v>11.0012</v>
       </c>
       <c r="F2" t="n">
-        <v>0.63</v>
+        <v>0.8317</v>
       </c>
       <c r="G2" t="n">
         <v>7.3399</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1054</v>
+        <v>0.1709</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1019</v>
+        <v>-0.0272</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0035</v>
+        <v>0.1981</v>
       </c>
       <c r="V2" t="n">
         <v>2.0026</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1379</v>
+        <v>4.335</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9442</v>
+        <v>5.0689</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1937</v>
+        <v>-0.7339</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3488</v>
+        <v>6.5673</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1212</v>
+        <v>5.6706</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2276</v>
+        <v>0.8968</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6703</v>
+        <v>8.4261</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8605</v>
+        <v>6.1576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8097</v>
+        <v>2.2685</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3215</v>
+        <v>-1.8587</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2606</v>
+        <v>-0.487</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5821</v>
+        <v>-1.3717</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0933</v>
+        <v>0.1415</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5059</v>
+        <v>0.1221</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5874</v>
+        <v>0.0193</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5882</v>
+        <v>3.6273</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9942</v>
+        <v>2.9358</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.406</v>
+        <v>0.6915</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5673</v>
+        <v>2.0676</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6706</v>
+        <v>0.4347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8968</v>
+        <v>1.6329</v>
       </c>
       <c r="J4" t="n">
-        <v>8.4261</v>
+        <v>2.6716</v>
       </c>
       <c r="K4" t="n">
-        <v>6.1576</v>
+        <v>0.3529</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2685</v>
+        <v>2.3187</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8587</v>
+        <v>-0.604</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.487</v>
+        <v>0.0818</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3717</v>
+        <v>-0.6859</v>
       </c>
       <c r="P4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6054</v>
+        <v>0.1808</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0474</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6528</v>
+        <v>0.275</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.214</v>
+        <v>2.5387</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1988</v>
+        <v>3.0441</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5072</v>
+        <v>2.3545</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6915</v>
+        <v>0.6896</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0676</v>
+        <v>1.3488</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4347</v>
+        <v>1.1212</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6329</v>
+        <v>0.2276</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6716</v>
+        <v>1.6703</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3529</v>
+        <v>0.8605</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3187</v>
+        <v>0.8097</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.604</v>
+        <v>-0.3215</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0818</v>
+        <v>0.2606</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6859</v>
+        <v>-0.5821</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2478</v>
+        <v>0.9994</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5228</v>
+        <v>0.9162</v>
       </c>
       <c r="U5" t="n">
-        <v>0.275</v>
+        <v>0.0833</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5387</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9438</v>
+        <v>1.6076</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4388</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.505</v>
+        <v>0.7403</v>
       </c>
       <c r="G6" t="n">
         <v>1.9443</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4643</v>
+        <v>0.1994</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5228</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0584</v>
+        <v>0.2937</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7699</v>
+        <v>-0.4441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0505</v>
+        <v>-0.6258</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7194</v>
+        <v>0.1817</v>
       </c>
       <c r="G7" t="n">
         <v>1.3303</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9215</v>
+        <v>0.7075</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4525</v>
+        <v>-0.2238</v>
       </c>
       <c r="U7" t="n">
-        <v>1.469</v>
+        <v>0.9313</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3943</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9712</v>
+        <v>-0.6895</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2587</v>
+        <v>-1.2614</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2299</v>
+        <v>0.5719</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5247</v>
+        <v>-0.2027</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5676</v>
+        <v>0.1921</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9571</v>
+        <v>-0.3948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.51</v>
+        <v>-0.8173</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.43</v>
+        <v>-0.215</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0347</v>
+        <v>0.6146</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1377</v>
+        <v>0.4071</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.897</v>
+        <v>0.2075</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5515</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0742</v>
+        <v>-0.3451</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2513</v>
+        <v>-0.2122</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3255</v>
+        <v>-0.1329</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1681</v>
+        <v>-0.8794</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.572</v>
+        <v>0.4514</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4039</v>
+        <v>-1.3307</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2027</v>
+        <v>-2.5247</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1921</v>
+        <v>-1.5676</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3948</v>
+        <v>-0.9571</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8173</v>
+        <v>0.51</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.215</v>
+        <v>-0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6146</v>
+        <v>-3.0347</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4071</v>
+        <v>-1.1377</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2075</v>
+        <v>-1.897</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5515</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8237</v>
+        <v>0.1661</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>-0.0587</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3009</v>
+        <v>0.2247</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3561</v>
+        <v>-3.9612</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6154</v>
+        <v>-4.1869</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2593</v>
+        <v>0.2257</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4598</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5768</v>
+        <v>-0.1819</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>-0.2436</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0953</v>
+        <v>0.0617</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.4842</v>
+        <v>-7.5104</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8806</v>
+        <v>-5.8059</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6036</v>
+        <v>-1.7045</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8651</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1489</v>
+        <v>0.1228</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1766</v>
+        <v>-0.1019</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3255</v>
+        <v>0.2247</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.2156</v>
+        <v>10.9623</v>
       </c>
       <c r="E12" t="n">
-        <v>10.0521</v>
+        <v>10.7992</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1633000000000002</v>
+        <v>0.1632999999999998</v>
       </c>
       <c r="G12" t="n">
         <v>11.5459</v>
@@ -1390,10 +1390,10 @@
         <v>12.7575</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4145</v>
+        <v>2.1614</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7645000000000002</v>
+        <v>-0.01749999999999995</v>
       </c>
       <c r="U12" t="n">
         <v>2.1789</v>
@@ -1405,7 +1405,7 @@
         <v>4.7142</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.139600000000001</v>
+        <v>-5.1396</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.033</v>
+        <v>2.3368</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2853</v>
+        <v>0.7571</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7477</v>
+        <v>1.5797</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6872</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2772</v>
+        <v>0.0266</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8883</v>
+        <v>-0.4165</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6111</v>
+        <v>0.443</v>
       </c>
       <c r="V13" t="n">
         <v>0.6778999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3493</v>
+        <v>0.4197</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8097</v>
+        <v>2.5714</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4604</v>
+        <v>-2.1517</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.6538</v>
+        <v>2.4213</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.1453</v>
+        <v>0.2029</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5085</v>
+        <v>2.2183</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6423</v>
+        <v>3.8764</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1674</v>
+        <v>1.1294</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8097</v>
+        <v>2.7469</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2961</v>
+        <v>-1.4551</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9779</v>
+        <v>-0.9265</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3182</v>
+        <v>-0.5286</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8587</v>
+        <v>-0.4835</v>
       </c>
       <c r="T14" t="n">
-        <v>2.041</v>
+        <v>-0.1452</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1823</v>
+        <v>-0.3383</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1444</v>
+        <v>-1.7501</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3603</v>
+        <v>-0.1112</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2176</v>
+        <v>2.1584</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5778</v>
+        <v>-2.2696</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4213</v>
+        <v>-2.6538</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2029</v>
+        <v>-2.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2183</v>
+        <v>-0.5085</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8764</v>
+        <v>0.6423</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1294</v>
+        <v>-0.1674</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7469</v>
+        <v>0.8097</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4551</v>
+        <v>-3.2961</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9265</v>
+        <v>-1.9779</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5286</v>
+        <v>-1.3182</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2634</v>
+        <v>0.3982</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4991</v>
+        <v>0.3896</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7644</v>
+        <v>0.0086</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7501</v>
+        <v>2.1444</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9257</v>
+        <v>-1.5833</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3104</v>
+        <v>1.4283</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2361</v>
+        <v>-3.0116</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2131</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4033</v>
+        <v>-0.0608</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4595</v>
+        <v>-0.3416</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0562</v>
+        <v>0.2807</v>
       </c>
       <c r="V16" t="n">
         <v>-2.3969</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1355</v>
+        <v>-2.1689</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1599</v>
+        <v>-2.1581</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0245</v>
+        <v>-0.0108</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.0562</v>
+        <v>-2.7248</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3866</v>
+        <v>-1.0384</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6697</v>
+        <v>-1.6864</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.5061</v>
+        <v>0.0165</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5223</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.9838</v>
+        <v>0.1069</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5501</v>
+        <v>-2.7413</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1357</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6859</v>
+        <v>-1.7933</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>2.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6888</v>
+        <v>-0.4441</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3462</v>
+        <v>-0.9274</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3427</v>
+        <v>0.4832</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8428</v>
+        <v>-2.4668</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.6155</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1094</v>
+        <v>-1.8513</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1632</v>
@@ -1858,13 +1858,13 @@
         <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6796</v>
+        <v>-0.3036</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4674</v>
+        <v>-0.3495</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2122</v>
+        <v>0.0459</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8766</v>
+        <v>-2.7417</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8659</v>
+        <v>-2.6317</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0108</v>
+        <v>-0.11</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7248</v>
+        <v>-3.0562</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0384</v>
+        <v>-1.3866</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6864</v>
+        <v>-1.6697</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0165</v>
+        <v>-2.5061</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-1.5223</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1069</v>
+        <v>-0.9838</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7413</v>
+        <v>-0.5501</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9481000000000001</v>
+        <v>0.1357</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7933</v>
+        <v>-0.6859</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7834</v>
+        <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1518</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.6351</v>
+        <v>-0.1256</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4832</v>
+        <v>0.2082</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.457</v>
+        <v>-3.1139</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0271</v>
+        <v>-1.6732</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4299</v>
+        <v>-1.4407</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4689</v>
@@ -2014,13 +2014,13 @@
         <v>2.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1867</v>
+        <v>0.1564</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6168</v>
+        <v>-0.2629</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4301</v>
+        <v>0.4193</v>
       </c>
       <c r="V20" t="n">
         <v>1.214</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.2156</v>
+        <v>-9.429299999999998</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1633000000000004</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.0522</v>
+        <v>-9.266</v>
       </c>
       <c r="G21" t="n">
         <v>-11.5459</v>
@@ -2092,13 +2092,13 @@
         <v>15.0769</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4145</v>
+        <v>-0.6282000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.179</v>
+        <v>-2.1791</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7644000000000001</v>
+        <v>1.5506</v>
       </c>
       <c r="V21" t="n">
         <v>0.4254</v>
